--- a/data/trans_dic/P19F$mañana-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P19F$mañana-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se cepilla los dientes por la mañana</t>
+          <t>Población que, al menos, se cepilla los dientes por la mañana (tasa de respuesta: 93,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>36,73; 47,27</t>
+          <t>37,45; 47,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>34,93; 44,69</t>
+          <t>34,6; 44,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37,13; 44,56</t>
+          <t>36,97; 44,21</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>34,22; 42,92</t>
+          <t>34,36; 42,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>40,73; 49,25</t>
+          <t>40,76; 49,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38,4; 44,69</t>
+          <t>38,75; 45,06</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29,37; 38,84</t>
+          <t>29,51; 39,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35,13; 44,81</t>
+          <t>34,76; 45,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33,54; 40,18</t>
+          <t>33,06; 40,25</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>44,21; 53,83</t>
+          <t>44,19; 53,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>49,35; 59,0</t>
+          <t>49,24; 59,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48,38; 55,15</t>
+          <t>48,28; 54,98</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>38,66; 43,19</t>
+          <t>38,16; 43,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>42,51; 47,35</t>
+          <t>42,49; 47,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41,32; 44,73</t>
+          <t>41,2; 44,52</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se cepilla los dientes por la mañana</t>
+          <t>Población que, al menos, se cepilla los dientes por la mañana (tasa de respuesta: 93,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>133235; 171455</t>
+          <t>135849; 173505</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>131374; 168095</t>
+          <t>130152; 168165</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>274324; 329221</t>
+          <t>273143; 326623</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>192748; 241730</t>
+          <t>193516; 240102</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>220197; 266225</t>
+          <t>220323; 267921</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423903; 493259</t>
+          <t>427710; 497334</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>118314; 156444</t>
+          <t>118877; 157234</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>134834; 171947</t>
+          <t>133379; 172885</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>263849; 316051</t>
+          <t>260037; 316568</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>198960; 242270</t>
+          <t>198871; 240915</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>218137; 260825</t>
+          <t>217645; 261317</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>431646; 492037</t>
+          <t>430724; 490509</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>687665; 768305</t>
+          <t>678823; 766106</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>740774; 825126</t>
+          <t>740350; 828265</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1455044; 1575069</t>
+          <t>1450680; 1567574</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19F$mañana-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P19F$mañana-Habitat-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>37,45; 47,83</t>
+          <t>37,35; 47,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>34,6; 44,71</t>
+          <t>34,55; 45,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36,97; 44,21</t>
+          <t>37,23; 44,42</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>34,36; 42,63</t>
+          <t>34,18; 42,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>40,76; 49,56</t>
+          <t>41,02; 49,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38,75; 45,06</t>
+          <t>38,5; 44,8</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29,51; 39,04</t>
+          <t>29,54; 39,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34,76; 45,05</t>
+          <t>34,42; 44,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33,06; 40,25</t>
+          <t>33,06; 40,19</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>44,19; 53,53</t>
+          <t>44,31; 53,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>49,24; 59,12</t>
+          <t>48,86; 59,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48,28; 54,98</t>
+          <t>48,06; 54,96</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>38,16; 43,07</t>
+          <t>38,71; 43,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>42,49; 47,53</t>
+          <t>42,57; 47,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41,2; 44,52</t>
+          <t>41,2; 44,45</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>135849; 173505</t>
+          <t>135465; 171079</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>130152; 168165</t>
+          <t>129969; 169831</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>273143; 326623</t>
+          <t>275100; 328174</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>193516; 240102</t>
+          <t>192499; 240354</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>220323; 267921</t>
+          <t>221733; 264893</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>427710; 497334</t>
+          <t>424903; 494470</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>118877; 157234</t>
+          <t>118996; 159280</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>133379; 172885</t>
+          <t>132099; 170542</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>260037; 316568</t>
+          <t>260016; 316118</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>198871; 240915</t>
+          <t>199445; 241942</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>217645; 261317</t>
+          <t>215982; 262265</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>430724; 490509</t>
+          <t>428716; 490327</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>678823; 766106</t>
+          <t>688651; 772357</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>740350; 828265</t>
+          <t>741817; 827572</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1450680; 1567574</t>
+          <t>1450668; 1565117</t>
         </is>
       </c>
     </row>
